--- a/DATA MASTER/Mei_25.xlsx
+++ b/DATA MASTER/Mei_25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BAM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96CC28D-5745-4324-968E-4AF599E57EDB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426B15BA-E2DE-4572-8F7A-94ABD7C3E70A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{702415C9-9CEC-41D8-A8F4-09C268C78C8C}"/>
   </bookViews>
